--- a/data/2026-05-03/BallparkPal_Games.xlsx
+++ b/data/2026-05-03/BallparkPal_Games.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
   <si>
     <t>GamePk</t>
   </si>
@@ -176,12 +176,36 @@
     <t>PIT</t>
   </si>
   <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
     <t>NYM</t>
   </si>
   <si>
     <t>LAA</t>
   </si>
   <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
@@ -192,6 +216,12 @@
   </si>
   <si>
     <t>CHC</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>BOS</t>
   </si>
   <si>
     <t>CLE</t>
@@ -537,7 +567,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -676,112 +706,112 @@
         <v>42</v>
       </c>
       <c r="E2">
-        <v>5.401</v>
+        <v>5.555</v>
       </c>
       <c r="F2">
-        <v>4.278</v>
+        <v>4.553</v>
       </c>
       <c r="G2">
-        <v>0.593</v>
+        <v>0.585</v>
       </c>
       <c r="H2">
-        <v>0.407</v>
+        <v>0.415</v>
       </c>
       <c r="I2">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="J2">
-        <v>0.099</v>
+        <v>0.094</v>
       </c>
       <c r="K2">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="L2">
-        <v>0.171</v>
+        <v>0.186</v>
       </c>
       <c r="M2">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="N2">
-        <v>0.155</v>
+        <v>0.15</v>
       </c>
       <c r="O2">
-        <v>0.545</v>
+        <v>0.572</v>
       </c>
       <c r="P2">
-        <v>3.111</v>
+        <v>3.17</v>
       </c>
       <c r="Q2">
-        <v>2.471</v>
+        <v>2.566</v>
       </c>
       <c r="R2">
-        <v>0.518</v>
+        <v>0.504</v>
       </c>
       <c r="S2">
-        <v>0.344</v>
+        <v>0.36</v>
       </c>
       <c r="T2">
         <v>0.0</v>
       </c>
       <c r="U2">
+        <v>0.008</v>
+      </c>
+      <c r="V2">
         <v>0.011</v>
       </c>
-      <c r="V2">
-        <v>0.012</v>
-      </c>
       <c r="W2">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="X2">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="Y2">
-        <v>0.082</v>
+        <v>0.07</v>
       </c>
       <c r="Z2">
-        <v>0.067</v>
+        <v>0.049</v>
       </c>
       <c r="AA2">
-        <v>0.101</v>
+        <v>0.097</v>
       </c>
       <c r="AB2">
+        <v>0.08</v>
+      </c>
+      <c r="AC2">
+        <v>0.108</v>
+      </c>
+      <c r="AD2">
         <v>0.075</v>
       </c>
-      <c r="AC2">
-        <v>0.113</v>
-      </c>
-      <c r="AD2">
-        <v>0.069</v>
-      </c>
       <c r="AE2">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="AF2">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AG2">
-        <v>0.059</v>
+        <v>0.071</v>
       </c>
       <c r="AH2">
-        <v>0.038</v>
+        <v>0.048</v>
       </c>
       <c r="AI2">
-        <v>0.045</v>
+        <v>0.048</v>
       </c>
       <c r="AJ2">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AK2">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AM2">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AN2">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="3" spans="1:40">
@@ -798,49 +828,49 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>4.541</v>
+        <v>4.276</v>
       </c>
       <c r="F3">
-        <v>4.923</v>
+        <v>4.95</v>
       </c>
       <c r="G3">
-        <v>0.432</v>
+        <v>0.407</v>
       </c>
       <c r="H3">
-        <v>0.568</v>
+        <v>0.593</v>
       </c>
       <c r="I3">
-        <v>0.233</v>
+        <v>0.209</v>
       </c>
       <c r="J3">
-        <v>0.085</v>
+        <v>0.081</v>
       </c>
       <c r="K3">
-        <v>0.115</v>
+        <v>0.118</v>
       </c>
       <c r="L3">
-        <v>0.279</v>
+        <v>0.299</v>
       </c>
       <c r="M3">
         <v>0.11</v>
       </c>
       <c r="N3">
-        <v>0.178</v>
+        <v>0.183</v>
       </c>
       <c r="O3">
-        <v>0.514</v>
+        <v>0.506</v>
       </c>
       <c r="P3">
-        <v>2.495</v>
+        <v>2.412</v>
       </c>
       <c r="Q3">
-        <v>2.946</v>
+        <v>2.999</v>
       </c>
       <c r="R3">
-        <v>0.379</v>
+        <v>0.365</v>
       </c>
       <c r="S3">
-        <v>0.478</v>
+        <v>0.494</v>
       </c>
       <c r="T3">
         <v>0.0</v>
@@ -849,40 +879,40 @@
         <v>0.011</v>
       </c>
       <c r="V3">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="W3">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="X3">
         <v>0.043</v>
       </c>
       <c r="Y3">
-        <v>0.082</v>
+        <v>0.096</v>
       </c>
       <c r="Z3">
-        <v>0.065</v>
+        <v>0.076</v>
       </c>
       <c r="AA3">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="AB3">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="AC3">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
       <c r="AD3">
-        <v>0.07</v>
+        <v>0.067</v>
       </c>
       <c r="AE3">
-        <v>0.088</v>
+        <v>0.083</v>
       </c>
       <c r="AF3">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="AG3">
-        <v>0.075</v>
+        <v>0.064</v>
       </c>
       <c r="AH3">
         <v>0.039</v>
@@ -891,19 +921,19 @@
         <v>0.035</v>
       </c>
       <c r="AJ3">
+        <v>0.022</v>
+      </c>
+      <c r="AK3">
         <v>0.019</v>
-      </c>
-      <c r="AK3">
-        <v>0.026</v>
       </c>
       <c r="AL3">
         <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AN3">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" spans="1:40">
@@ -920,112 +950,112 @@
         <v>46</v>
       </c>
       <c r="E4">
-        <v>5.181</v>
+        <v>5.631</v>
       </c>
       <c r="F4">
-        <v>4.021</v>
+        <v>4.267</v>
       </c>
       <c r="G4">
-        <v>0.591</v>
+        <v>0.61</v>
       </c>
       <c r="H4">
-        <v>0.409</v>
+        <v>0.39</v>
       </c>
       <c r="I4">
-        <v>0.356</v>
+        <v>0.387</v>
       </c>
       <c r="J4">
-        <v>0.113</v>
+        <v>0.107</v>
       </c>
       <c r="K4">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="L4">
-        <v>0.173</v>
+        <v>0.169</v>
       </c>
       <c r="M4">
-        <v>0.08</v>
+        <v>0.084</v>
       </c>
       <c r="N4">
-        <v>0.156</v>
+        <v>0.136</v>
       </c>
       <c r="O4">
-        <v>0.549</v>
+        <v>0.556</v>
       </c>
       <c r="P4">
-        <v>2.884</v>
+        <v>3.002</v>
       </c>
       <c r="Q4">
-        <v>2.322</v>
+        <v>2.475</v>
       </c>
       <c r="R4">
-        <v>0.495</v>
+        <v>0.491</v>
       </c>
       <c r="S4">
-        <v>0.353</v>
+        <v>0.365</v>
       </c>
       <c r="T4">
         <v>0.0</v>
       </c>
       <c r="U4">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="V4">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="W4">
-        <v>0.057</v>
+        <v>0.035</v>
       </c>
       <c r="X4">
-        <v>0.048</v>
+        <v>0.035</v>
       </c>
       <c r="Y4">
-        <v>0.086</v>
+        <v>0.076</v>
       </c>
       <c r="Z4">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
       <c r="AA4">
         <v>0.098</v>
       </c>
       <c r="AB4">
+        <v>0.074</v>
+      </c>
+      <c r="AC4">
+        <v>0.102</v>
+      </c>
+      <c r="AD4">
+        <v>0.081</v>
+      </c>
+      <c r="AE4">
         <v>0.083</v>
       </c>
-      <c r="AC4">
-        <v>0.11</v>
-      </c>
-      <c r="AD4">
-        <v>0.07</v>
-      </c>
-      <c r="AE4">
-        <v>0.079</v>
-      </c>
       <c r="AF4">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="AG4">
-        <v>0.061</v>
+        <v>0.074</v>
       </c>
       <c r="AH4">
-        <v>0.03</v>
+        <v>0.041</v>
       </c>
       <c r="AI4">
-        <v>0.037</v>
+        <v>0.045</v>
       </c>
       <c r="AJ4">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="AK4">
-        <v>0.019</v>
+        <v>0.031</v>
       </c>
       <c r="AL4">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="AM4">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="AN4">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="5" spans="1:40">
@@ -1042,70 +1072,70 @@
         <v>48</v>
       </c>
       <c r="E5">
-        <v>4.013</v>
+        <v>4.343</v>
       </c>
       <c r="F5">
-        <v>4.191</v>
+        <v>4.309</v>
       </c>
       <c r="G5">
-        <v>0.461</v>
+        <v>0.472</v>
       </c>
       <c r="H5">
-        <v>0.539</v>
+        <v>0.528</v>
       </c>
       <c r="I5">
-        <v>0.243</v>
+        <v>0.256</v>
       </c>
       <c r="J5">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="K5">
-        <v>0.122</v>
+        <v>0.125</v>
       </c>
       <c r="L5">
-        <v>0.25</v>
+        <v>0.241</v>
       </c>
       <c r="M5">
-        <v>0.113</v>
+        <v>0.114</v>
       </c>
       <c r="N5">
-        <v>0.176</v>
+        <v>0.172</v>
       </c>
       <c r="O5">
-        <v>0.504</v>
+        <v>0.515</v>
       </c>
       <c r="P5">
-        <v>2.28</v>
+        <v>2.434</v>
       </c>
       <c r="Q5">
-        <v>2.359</v>
+        <v>2.421</v>
       </c>
       <c r="R5">
+        <v>0.43</v>
+      </c>
+      <c r="S5">
         <v>0.421</v>
-      </c>
-      <c r="S5">
-        <v>0.42</v>
       </c>
       <c r="T5">
         <v>0.0</v>
       </c>
       <c r="U5">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="V5">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="W5">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="X5">
-        <v>0.063</v>
+        <v>0.053</v>
       </c>
       <c r="Y5">
-        <v>0.107</v>
+        <v>0.098</v>
       </c>
       <c r="Z5">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="AA5">
         <v>0.12</v>
@@ -1114,40 +1144,40 @@
         <v>0.091</v>
       </c>
       <c r="AC5">
-        <v>0.105</v>
+        <v>0.108</v>
       </c>
       <c r="AD5">
-        <v>0.066</v>
+        <v>0.068</v>
       </c>
       <c r="AE5">
-        <v>0.071</v>
+        <v>0.075</v>
       </c>
       <c r="AF5">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="AG5">
-        <v>0.042</v>
+        <v>0.055</v>
       </c>
       <c r="AH5">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="AI5">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
       <c r="AJ5">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AK5">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="AL5">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AM5">
         <v>0.009</v>
       </c>
       <c r="AN5">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="6" spans="1:40">
@@ -1164,112 +1194,112 @@
         <v>50</v>
       </c>
       <c r="E6">
-        <v>3.683</v>
+        <v>3.825</v>
       </c>
       <c r="F6">
-        <v>5.628</v>
+        <v>5.675</v>
       </c>
       <c r="G6">
-        <v>0.288</v>
+        <v>0.295</v>
       </c>
       <c r="H6">
-        <v>0.712</v>
+        <v>0.705</v>
       </c>
       <c r="I6">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="J6">
-        <v>0.056</v>
+        <v>0.069</v>
       </c>
       <c r="K6">
-        <v>0.093</v>
+        <v>0.088</v>
       </c>
       <c r="L6">
-        <v>0.43</v>
+        <v>0.424</v>
       </c>
       <c r="M6">
-        <v>0.109</v>
+        <v>0.112</v>
       </c>
       <c r="N6">
-        <v>0.172</v>
+        <v>0.169</v>
       </c>
       <c r="O6">
-        <v>0.527</v>
+        <v>0.537</v>
       </c>
       <c r="P6">
-        <v>1.982</v>
+        <v>2.088</v>
       </c>
       <c r="Q6">
-        <v>3.616</v>
+        <v>3.576</v>
       </c>
       <c r="R6">
-        <v>0.252</v>
+        <v>0.266</v>
       </c>
       <c r="S6">
-        <v>0.622</v>
+        <v>0.618</v>
       </c>
       <c r="T6">
         <v>0.0</v>
       </c>
       <c r="U6">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="V6">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="W6">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="X6">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
       <c r="Y6">
-        <v>0.085</v>
+        <v>0.075</v>
       </c>
       <c r="Z6">
-        <v>0.066</v>
+        <v>0.069</v>
       </c>
       <c r="AA6">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="AB6">
-        <v>0.085</v>
+        <v>0.076</v>
       </c>
       <c r="AC6">
-        <v>0.11</v>
+        <v>0.099</v>
       </c>
       <c r="AD6">
-        <v>0.07</v>
+        <v>0.069</v>
       </c>
       <c r="AE6">
-        <v>0.084</v>
+        <v>0.094</v>
       </c>
       <c r="AF6">
-        <v>0.05</v>
+        <v>0.056</v>
       </c>
       <c r="AG6">
-        <v>0.061</v>
+        <v>0.067</v>
       </c>
       <c r="AH6">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AI6">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="AJ6">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="AK6">
         <v>0.024</v>
       </c>
       <c r="AL6">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AM6">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AN6">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="7" spans="1:40">
@@ -1286,117 +1316,117 @@
         <v>52</v>
       </c>
       <c r="E7">
-        <v>3.56</v>
+        <v>3.608</v>
       </c>
       <c r="F7">
-        <v>3.846</v>
+        <v>4.247</v>
       </c>
       <c r="G7">
-        <v>0.442</v>
+        <v>0.413</v>
       </c>
       <c r="H7">
-        <v>0.558</v>
+        <v>0.587</v>
       </c>
       <c r="I7">
-        <v>0.209</v>
+        <v>0.203</v>
       </c>
       <c r="J7">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K7">
-        <v>0.133</v>
+        <v>0.121</v>
       </c>
       <c r="L7">
-        <v>0.246</v>
+        <v>0.292</v>
       </c>
       <c r="M7">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="N7">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="O7">
-        <v>0.368</v>
+        <v>0.396</v>
       </c>
       <c r="P7">
-        <v>1.739</v>
+        <v>1.756</v>
       </c>
       <c r="Q7">
-        <v>1.949</v>
+        <v>2.158</v>
       </c>
       <c r="R7">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="S7">
-        <v>0.433</v>
+        <v>0.446</v>
       </c>
       <c r="T7">
         <v>0.0</v>
       </c>
       <c r="U7">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="V7">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="W7">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="X7">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
       <c r="Y7">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="Z7">
-        <v>0.087</v>
+        <v>0.079</v>
       </c>
       <c r="AA7">
-        <v>0.123</v>
+        <v>0.134</v>
       </c>
       <c r="AB7">
-        <v>0.079</v>
+        <v>0.086</v>
       </c>
       <c r="AC7">
-        <v>0.108</v>
+        <v>0.093</v>
       </c>
       <c r="AD7">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
       <c r="AE7">
-        <v>0.057</v>
+        <v>0.068</v>
       </c>
       <c r="AF7">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="AG7">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AH7">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="AI7">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AJ7">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="AK7">
-        <v>0.009</v>
+        <v>0.014</v>
       </c>
       <c r="AL7">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AM7">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AN7">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8">
-        <v>824043</v>
+        <v>823555</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
@@ -1408,117 +1438,117 @@
         <v>54</v>
       </c>
       <c r="E8">
-        <v>5.93</v>
+        <v>4.031</v>
       </c>
       <c r="F8">
-        <v>5.115</v>
+        <v>5.19</v>
       </c>
       <c r="G8">
-        <v>0.556</v>
+        <v>0.352</v>
       </c>
       <c r="H8">
-        <v>0.444</v>
+        <v>0.648</v>
       </c>
       <c r="I8">
-        <v>0.352</v>
+        <v>0.178</v>
       </c>
       <c r="J8">
-        <v>0.087</v>
+        <v>0.073</v>
       </c>
       <c r="K8">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="L8">
-        <v>0.207</v>
+        <v>0.353</v>
       </c>
       <c r="M8">
-        <v>0.097</v>
+        <v>0.117</v>
       </c>
       <c r="N8">
-        <v>0.139</v>
+        <v>0.178</v>
       </c>
       <c r="O8">
-        <v>0.591</v>
+        <v>0.531</v>
       </c>
       <c r="P8">
-        <v>3.54</v>
+        <v>2.098</v>
       </c>
       <c r="Q8">
-        <v>2.961</v>
+        <v>3.189</v>
       </c>
       <c r="R8">
-        <v>0.506</v>
+        <v>0.304</v>
       </c>
       <c r="S8">
-        <v>0.363</v>
+        <v>0.559</v>
       </c>
       <c r="T8">
         <v>0.0</v>
       </c>
       <c r="U8">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="V8">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="W8">
+        <v>0.048</v>
+      </c>
+      <c r="X8">
+        <v>0.051</v>
+      </c>
+      <c r="Y8">
+        <v>0.097</v>
+      </c>
+      <c r="Z8">
+        <v>0.073</v>
+      </c>
+      <c r="AA8">
+        <v>0.107</v>
+      </c>
+      <c r="AB8">
+        <v>0.081</v>
+      </c>
+      <c r="AC8">
+        <v>0.098</v>
+      </c>
+      <c r="AD8">
+        <v>0.068</v>
+      </c>
+      <c r="AE8">
+        <v>0.079</v>
+      </c>
+      <c r="AF8">
+        <v>0.055</v>
+      </c>
+      <c r="AG8">
+        <v>0.06</v>
+      </c>
+      <c r="AH8">
+        <v>0.03</v>
+      </c>
+      <c r="AI8">
+        <v>0.039</v>
+      </c>
+      <c r="AJ8">
+        <v>0.019</v>
+      </c>
+      <c r="AK8">
         <v>0.024</v>
       </c>
-      <c r="X8">
-        <v>0.024</v>
-      </c>
-      <c r="Y8">
-        <v>0.048</v>
-      </c>
-      <c r="Z8">
-        <v>0.047</v>
-      </c>
-      <c r="AA8">
-        <v>0.093</v>
-      </c>
-      <c r="AB8">
-        <v>0.069</v>
-      </c>
-      <c r="AC8">
-        <v>0.102</v>
-      </c>
-      <c r="AD8">
-        <v>0.077</v>
-      </c>
-      <c r="AE8">
-        <v>0.094</v>
-      </c>
-      <c r="AF8">
-        <v>0.06</v>
-      </c>
-      <c r="AG8">
-        <v>0.082</v>
-      </c>
-      <c r="AH8">
-        <v>0.056</v>
-      </c>
-      <c r="AI8">
-        <v>0.047</v>
-      </c>
-      <c r="AJ8">
-        <v>0.036</v>
-      </c>
-      <c r="AK8">
-        <v>0.029</v>
-      </c>
       <c r="AL8">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="AM8">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="AN8">
-        <v>0.054</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9">
-        <v>824364</v>
+        <v>823711</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1530,117 +1560,117 @@
         <v>56</v>
       </c>
       <c r="E9">
-        <v>6.248</v>
+        <v>4.51</v>
       </c>
       <c r="F9">
-        <v>6.373</v>
+        <v>4.418</v>
       </c>
       <c r="G9">
-        <v>0.465</v>
+        <v>0.495</v>
       </c>
       <c r="H9">
-        <v>0.535</v>
+        <v>0.505</v>
       </c>
       <c r="I9">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="J9">
-        <v>0.084</v>
+        <v>0.102</v>
       </c>
       <c r="K9">
-        <v>0.096</v>
+        <v>0.128</v>
       </c>
       <c r="L9">
-        <v>0.3</v>
+        <v>0.234</v>
       </c>
       <c r="M9">
-        <v>0.088</v>
+        <v>0.094</v>
       </c>
       <c r="N9">
-        <v>0.147</v>
+        <v>0.177</v>
       </c>
       <c r="O9">
-        <v>0.622</v>
+        <v>0.493</v>
       </c>
       <c r="P9">
-        <v>3.366</v>
+        <v>2.199</v>
       </c>
       <c r="Q9">
-        <v>4.071</v>
+        <v>2.43</v>
       </c>
       <c r="R9">
-        <v>0.368</v>
+        <v>0.398</v>
       </c>
       <c r="S9">
-        <v>0.53</v>
+        <v>0.445</v>
       </c>
       <c r="T9">
         <v>0.0</v>
       </c>
       <c r="U9">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="V9">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="W9">
+        <v>0.055</v>
+      </c>
+      <c r="X9">
+        <v>0.045</v>
+      </c>
+      <c r="Y9">
+        <v>0.103</v>
+      </c>
+      <c r="Z9">
+        <v>0.07</v>
+      </c>
+      <c r="AA9">
+        <v>0.114</v>
+      </c>
+      <c r="AB9">
+        <v>0.086</v>
+      </c>
+      <c r="AC9">
+        <v>0.101</v>
+      </c>
+      <c r="AD9">
+        <v>0.064</v>
+      </c>
+      <c r="AE9">
+        <v>0.08</v>
+      </c>
+      <c r="AF9">
+        <v>0.052</v>
+      </c>
+      <c r="AG9">
+        <v>0.05</v>
+      </c>
+      <c r="AH9">
+        <v>0.03</v>
+      </c>
+      <c r="AI9">
+        <v>0.033</v>
+      </c>
+      <c r="AJ9">
+        <v>0.024</v>
+      </c>
+      <c r="AK9">
+        <v>0.017</v>
+      </c>
+      <c r="AL9">
+        <v>0.013</v>
+      </c>
+      <c r="AM9">
         <v>0.011</v>
       </c>
-      <c r="X9">
-        <v>0.014</v>
-      </c>
-      <c r="Y9">
-        <v>0.035</v>
-      </c>
-      <c r="Z9">
-        <v>0.033</v>
-      </c>
-      <c r="AA9">
-        <v>0.059</v>
-      </c>
-      <c r="AB9">
-        <v>0.054</v>
-      </c>
-      <c r="AC9">
-        <v>0.09</v>
-      </c>
-      <c r="AD9">
-        <v>0.058</v>
-      </c>
-      <c r="AE9">
-        <v>0.091</v>
-      </c>
-      <c r="AF9">
-        <v>0.068</v>
-      </c>
-      <c r="AG9">
-        <v>0.081</v>
-      </c>
-      <c r="AH9">
-        <v>0.062</v>
-      </c>
-      <c r="AI9">
-        <v>0.068</v>
-      </c>
-      <c r="AJ9">
-        <v>0.057</v>
-      </c>
-      <c r="AK9">
-        <v>0.05</v>
-      </c>
-      <c r="AL9">
-        <v>0.031</v>
-      </c>
-      <c r="AM9">
-        <v>0.04</v>
-      </c>
       <c r="AN9">
-        <v>0.09</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="10" spans="1:40">
       <c r="A10">
-        <v>824687</v>
+        <v>823875</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1652,117 +1682,117 @@
         <v>58</v>
       </c>
       <c r="E10">
-        <v>5.453</v>
+        <v>4.457</v>
       </c>
       <c r="F10">
-        <v>6.296</v>
+        <v>3.71</v>
       </c>
       <c r="G10">
-        <v>0.396</v>
+        <v>0.563</v>
       </c>
       <c r="H10">
-        <v>0.604</v>
+        <v>0.437</v>
       </c>
       <c r="I10">
-        <v>0.218</v>
+        <v>0.301</v>
       </c>
       <c r="J10">
-        <v>0.079</v>
+        <v>0.121</v>
       </c>
       <c r="K10">
-        <v>0.099</v>
+        <v>0.141</v>
       </c>
       <c r="L10">
-        <v>0.341</v>
+        <v>0.176</v>
       </c>
       <c r="M10">
-        <v>0.11</v>
+        <v>0.084</v>
       </c>
       <c r="N10">
-        <v>0.153</v>
+        <v>0.177</v>
       </c>
       <c r="O10">
-        <v>0.6</v>
+        <v>0.459</v>
       </c>
       <c r="P10">
-        <v>3.092</v>
+        <v>2.423</v>
       </c>
       <c r="Q10">
-        <v>4.027</v>
+        <v>1.962</v>
       </c>
       <c r="R10">
-        <v>0.348</v>
+        <v>0.474</v>
       </c>
       <c r="S10">
-        <v>0.543</v>
+        <v>0.354</v>
       </c>
       <c r="T10">
-        <v>0.0</v>
+        <v>0.001</v>
       </c>
       <c r="U10">
-        <v>0.002</v>
+        <v>0.023</v>
       </c>
       <c r="V10">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="W10">
-        <v>0.018</v>
+        <v>0.073</v>
       </c>
       <c r="X10">
-        <v>0.023</v>
+        <v>0.066</v>
       </c>
       <c r="Y10">
-        <v>0.041</v>
+        <v>0.101</v>
       </c>
       <c r="Z10">
+        <v>0.078</v>
+      </c>
+      <c r="AA10">
+        <v>0.121</v>
+      </c>
+      <c r="AB10">
+        <v>0.083</v>
+      </c>
+      <c r="AC10">
+        <v>0.097</v>
+      </c>
+      <c r="AD10">
+        <v>0.067</v>
+      </c>
+      <c r="AE10">
+        <v>0.077</v>
+      </c>
+      <c r="AF10">
+        <v>0.047</v>
+      </c>
+      <c r="AG10">
         <v>0.044</v>
       </c>
-      <c r="AA10">
-        <v>0.066</v>
-      </c>
-      <c r="AB10">
-        <v>0.062</v>
-      </c>
-      <c r="AC10">
-        <v>0.093</v>
-      </c>
-      <c r="AD10">
-        <v>0.074</v>
-      </c>
-      <c r="AE10">
-        <v>0.097</v>
-      </c>
-      <c r="AF10">
-        <v>0.065</v>
-      </c>
-      <c r="AG10">
-        <v>0.082</v>
-      </c>
       <c r="AH10">
-        <v>0.06</v>
+        <v>0.024</v>
       </c>
       <c r="AI10">
-        <v>0.063</v>
+        <v>0.027</v>
       </c>
       <c r="AJ10">
-        <v>0.043</v>
+        <v>0.015</v>
       </c>
       <c r="AK10">
-        <v>0.048</v>
+        <v>0.012</v>
       </c>
       <c r="AL10">
-        <v>0.023</v>
+        <v>0.006</v>
       </c>
       <c r="AM10">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="AN10">
-        <v>0.068</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="11" spans="1:40">
       <c r="A11">
-        <v>825013</v>
+        <v>824043</v>
       </c>
       <c r="B11" t="s">
         <v>40</v>
@@ -1774,112 +1804,722 @@
         <v>60</v>
       </c>
       <c r="E11">
-        <v>4.938</v>
+        <v>5.875</v>
       </c>
       <c r="F11">
-        <v>4.34</v>
+        <v>4.991</v>
       </c>
       <c r="G11">
-        <v>0.532</v>
+        <v>0.553</v>
       </c>
       <c r="H11">
-        <v>0.468</v>
+        <v>0.447</v>
       </c>
       <c r="I11">
-        <v>0.312</v>
+        <v>0.364</v>
       </c>
       <c r="J11">
-        <v>0.105</v>
+        <v>0.085</v>
       </c>
       <c r="K11">
-        <v>0.116</v>
+        <v>0.104</v>
       </c>
       <c r="L11">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="M11">
-        <v>0.092</v>
+        <v>0.085</v>
       </c>
       <c r="N11">
-        <v>0.168</v>
+        <v>0.149</v>
       </c>
       <c r="O11">
-        <v>0.48</v>
+        <v>0.583</v>
       </c>
       <c r="P11">
-        <v>2.684</v>
+        <v>3.437</v>
       </c>
       <c r="Q11">
-        <v>2.23</v>
+        <v>2.893</v>
       </c>
       <c r="R11">
-        <v>0.491</v>
+        <v>0.499</v>
       </c>
       <c r="S11">
-        <v>0.362</v>
+        <v>0.378</v>
       </c>
       <c r="T11">
         <v>0.0</v>
       </c>
       <c r="U11">
+        <v>0.003</v>
+      </c>
+      <c r="V11">
+        <v>0.008</v>
+      </c>
+      <c r="W11">
+        <v>0.022</v>
+      </c>
+      <c r="X11">
+        <v>0.026</v>
+      </c>
+      <c r="Y11">
+        <v>0.065</v>
+      </c>
+      <c r="Z11">
+        <v>0.045</v>
+      </c>
+      <c r="AA11">
+        <v>0.083</v>
+      </c>
+      <c r="AB11">
+        <v>0.066</v>
+      </c>
+      <c r="AC11">
+        <v>0.103</v>
+      </c>
+      <c r="AD11">
+        <v>0.082</v>
+      </c>
+      <c r="AE11">
+        <v>0.093</v>
+      </c>
+      <c r="AF11">
+        <v>0.067</v>
+      </c>
+      <c r="AG11">
+        <v>0.081</v>
+      </c>
+      <c r="AH11">
+        <v>0.051</v>
+      </c>
+      <c r="AI11">
+        <v>0.053</v>
+      </c>
+      <c r="AJ11">
+        <v>0.029</v>
+      </c>
+      <c r="AK11">
+        <v>0.041</v>
+      </c>
+      <c r="AL11">
+        <v>0.02</v>
+      </c>
+      <c r="AM11">
+        <v>0.02</v>
+      </c>
+      <c r="AN11">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40">
+      <c r="A12">
+        <v>824285</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12">
+        <v>5.153</v>
+      </c>
+      <c r="F12">
+        <v>5.005</v>
+      </c>
+      <c r="G12">
+        <v>0.481</v>
+      </c>
+      <c r="H12">
+        <v>0.519</v>
+      </c>
+      <c r="I12">
+        <v>0.289</v>
+      </c>
+      <c r="J12">
+        <v>0.084</v>
+      </c>
+      <c r="K12">
+        <v>0.107</v>
+      </c>
+      <c r="L12">
+        <v>0.267</v>
+      </c>
+      <c r="M12">
+        <v>0.088</v>
+      </c>
+      <c r="N12">
+        <v>0.164</v>
+      </c>
+      <c r="O12">
+        <v>0.548</v>
+      </c>
+      <c r="P12">
+        <v>2.844</v>
+      </c>
+      <c r="Q12">
+        <v>2.902</v>
+      </c>
+      <c r="R12">
+        <v>0.436</v>
+      </c>
+      <c r="S12">
+        <v>0.443</v>
+      </c>
+      <c r="T12">
+        <v>0.0</v>
+      </c>
+      <c r="U12">
+        <v>0.009</v>
+      </c>
+      <c r="V12">
         <v>0.01</v>
       </c>
-      <c r="V11">
+      <c r="W12">
+        <v>0.04</v>
+      </c>
+      <c r="X12">
+        <v>0.033</v>
+      </c>
+      <c r="Y12">
+        <v>0.079</v>
+      </c>
+      <c r="Z12">
+        <v>0.054</v>
+      </c>
+      <c r="AA12">
+        <v>0.095</v>
+      </c>
+      <c r="AB12">
+        <v>0.071</v>
+      </c>
+      <c r="AC12">
+        <v>0.105</v>
+      </c>
+      <c r="AD12">
+        <v>0.083</v>
+      </c>
+      <c r="AE12">
+        <v>0.091</v>
+      </c>
+      <c r="AF12">
+        <v>0.054</v>
+      </c>
+      <c r="AG12">
+        <v>0.063</v>
+      </c>
+      <c r="AH12">
+        <v>0.041</v>
+      </c>
+      <c r="AI12">
+        <v>0.046</v>
+      </c>
+      <c r="AJ12">
+        <v>0.024</v>
+      </c>
+      <c r="AK12">
+        <v>0.027</v>
+      </c>
+      <c r="AL12">
         <v>0.016</v>
       </c>
-      <c r="W11">
-        <v>0.046</v>
-      </c>
-      <c r="X11">
+      <c r="AM12">
+        <v>0.019</v>
+      </c>
+      <c r="AN12">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13">
+        <v>824364</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>6.047</v>
+      </c>
+      <c r="F13">
+        <v>6.473</v>
+      </c>
+      <c r="G13">
+        <v>0.442</v>
+      </c>
+      <c r="H13">
+        <v>0.558</v>
+      </c>
+      <c r="I13">
+        <v>0.259</v>
+      </c>
+      <c r="J13">
+        <v>0.089</v>
+      </c>
+      <c r="K13">
+        <v>0.094</v>
+      </c>
+      <c r="L13">
+        <v>0.317</v>
+      </c>
+      <c r="M13">
+        <v>0.093</v>
+      </c>
+      <c r="N13">
+        <v>0.148</v>
+      </c>
+      <c r="O13">
+        <v>0.631</v>
+      </c>
+      <c r="P13">
+        <v>3.25</v>
+      </c>
+      <c r="Q13">
+        <v>4.083</v>
+      </c>
+      <c r="R13">
+        <v>0.36</v>
+      </c>
+      <c r="S13">
+        <v>0.533</v>
+      </c>
+      <c r="T13">
+        <v>0.0</v>
+      </c>
+      <c r="U13">
+        <v>0.003</v>
+      </c>
+      <c r="V13">
+        <v>0.003</v>
+      </c>
+      <c r="W13">
+        <v>0.013</v>
+      </c>
+      <c r="X13">
+        <v>0.015</v>
+      </c>
+      <c r="Y13">
+        <v>0.03</v>
+      </c>
+      <c r="Z13">
+        <v>0.037</v>
+      </c>
+      <c r="AA13">
+        <v>0.065</v>
+      </c>
+      <c r="AB13">
+        <v>0.056</v>
+      </c>
+      <c r="AC13">
+        <v>0.079</v>
+      </c>
+      <c r="AD13">
+        <v>0.071</v>
+      </c>
+      <c r="AE13">
+        <v>0.09</v>
+      </c>
+      <c r="AF13">
+        <v>0.066</v>
+      </c>
+      <c r="AG13">
+        <v>0.088</v>
+      </c>
+      <c r="AH13">
+        <v>0.055</v>
+      </c>
+      <c r="AI13">
+        <v>0.071</v>
+      </c>
+      <c r="AJ13">
         <v>0.05</v>
       </c>
-      <c r="Y11">
+      <c r="AK13">
+        <v>0.059</v>
+      </c>
+      <c r="AL13">
+        <v>0.031</v>
+      </c>
+      <c r="AM13">
+        <v>0.036</v>
+      </c>
+      <c r="AN13">
+        <v>0.085</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14">
+        <v>824687</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14">
+        <v>6.42</v>
+      </c>
+      <c r="F14">
+        <v>7.5</v>
+      </c>
+      <c r="G14">
+        <v>0.377</v>
+      </c>
+      <c r="H14">
+        <v>0.623</v>
+      </c>
+      <c r="I14">
+        <v>0.24</v>
+      </c>
+      <c r="J14">
+        <v>0.055</v>
+      </c>
+      <c r="K14">
+        <v>0.082</v>
+      </c>
+      <c r="L14">
+        <v>0.375</v>
+      </c>
+      <c r="M14">
+        <v>0.095</v>
+      </c>
+      <c r="N14">
+        <v>0.153</v>
+      </c>
+      <c r="O14">
+        <v>0.642</v>
+      </c>
+      <c r="P14">
+        <v>3.632</v>
+      </c>
+      <c r="Q14">
+        <v>4.746</v>
+      </c>
+      <c r="R14">
+        <v>0.338</v>
+      </c>
+      <c r="S14">
+        <v>0.552</v>
+      </c>
+      <c r="T14">
+        <v>0.0</v>
+      </c>
+      <c r="U14">
+        <v>0.0</v>
+      </c>
+      <c r="V14">
+        <v>0.0</v>
+      </c>
+      <c r="W14">
+        <v>0.01</v>
+      </c>
+      <c r="X14">
+        <v>0.008</v>
+      </c>
+      <c r="Y14">
+        <v>0.026</v>
+      </c>
+      <c r="Z14">
+        <v>0.026</v>
+      </c>
+      <c r="AA14">
+        <v>0.044</v>
+      </c>
+      <c r="AB14">
+        <v>0.041</v>
+      </c>
+      <c r="AC14">
+        <v>0.069</v>
+      </c>
+      <c r="AD14">
+        <v>0.058</v>
+      </c>
+      <c r="AE14">
+        <v>0.081</v>
+      </c>
+      <c r="AF14">
+        <v>0.054</v>
+      </c>
+      <c r="AG14">
+        <v>0.088</v>
+      </c>
+      <c r="AH14">
+        <v>0.059</v>
+      </c>
+      <c r="AI14">
+        <v>0.08</v>
+      </c>
+      <c r="AJ14">
+        <v>0.053</v>
+      </c>
+      <c r="AK14">
+        <v>0.058</v>
+      </c>
+      <c r="AL14">
+        <v>0.043</v>
+      </c>
+      <c r="AM14">
+        <v>0.053</v>
+      </c>
+      <c r="AN14">
+        <v>0.147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15">
+        <v>824769</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15">
+        <v>5.424</v>
+      </c>
+      <c r="F15">
+        <v>5.594</v>
+      </c>
+      <c r="G15">
+        <v>0.444</v>
+      </c>
+      <c r="H15">
+        <v>0.556</v>
+      </c>
+      <c r="I15">
+        <v>0.259</v>
+      </c>
+      <c r="J15">
+        <v>0.084</v>
+      </c>
+      <c r="K15">
+        <v>0.102</v>
+      </c>
+      <c r="L15">
+        <v>0.286</v>
+      </c>
+      <c r="M15">
+        <v>0.096</v>
+      </c>
+      <c r="N15">
+        <v>0.174</v>
+      </c>
+      <c r="O15">
+        <v>0.602</v>
+      </c>
+      <c r="P15">
+        <v>3.095</v>
+      </c>
+      <c r="Q15">
+        <v>3.388</v>
+      </c>
+      <c r="R15">
+        <v>0.403</v>
+      </c>
+      <c r="S15">
+        <v>0.473</v>
+      </c>
+      <c r="T15">
+        <v>0.0</v>
+      </c>
+      <c r="U15">
+        <v>0.004</v>
+      </c>
+      <c r="V15">
+        <v>0.006</v>
+      </c>
+      <c r="W15">
+        <v>0.026</v>
+      </c>
+      <c r="X15">
+        <v>0.021</v>
+      </c>
+      <c r="Y15">
+        <v>0.057</v>
+      </c>
+      <c r="Z15">
+        <v>0.053</v>
+      </c>
+      <c r="AA15">
         <v>0.089</v>
       </c>
-      <c r="Z11">
-        <v>0.072</v>
-      </c>
-      <c r="AA11">
-        <v>0.11</v>
-      </c>
-      <c r="AB11">
+      <c r="AB15">
+        <v>0.067</v>
+      </c>
+      <c r="AC15">
+        <v>0.095</v>
+      </c>
+      <c r="AD15">
         <v>0.078</v>
       </c>
-      <c r="AC11">
-        <v>0.107</v>
-      </c>
-      <c r="AD11">
-        <v>0.072</v>
-      </c>
-      <c r="AE11">
+      <c r="AE15">
+        <v>0.091</v>
+      </c>
+      <c r="AF15">
+        <v>0.06</v>
+      </c>
+      <c r="AG15">
+        <v>0.083</v>
+      </c>
+      <c r="AH15">
+        <v>0.047</v>
+      </c>
+      <c r="AI15">
+        <v>0.059</v>
+      </c>
+      <c r="AJ15">
+        <v>0.029</v>
+      </c>
+      <c r="AK15">
+        <v>0.041</v>
+      </c>
+      <c r="AL15">
+        <v>0.022</v>
+      </c>
+      <c r="AM15">
+        <v>0.016</v>
+      </c>
+      <c r="AN15">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
+      <c r="A16">
+        <v>825013</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16">
+        <v>5.169</v>
+      </c>
+      <c r="F16">
+        <v>4.726</v>
+      </c>
+      <c r="G16">
+        <v>0.521</v>
+      </c>
+      <c r="H16">
+        <v>0.479</v>
+      </c>
+      <c r="I16">
+        <v>0.299</v>
+      </c>
+      <c r="J16">
+        <v>0.106</v>
+      </c>
+      <c r="K16">
+        <v>0.116</v>
+      </c>
+      <c r="L16">
+        <v>0.221</v>
+      </c>
+      <c r="M16">
+        <v>0.097</v>
+      </c>
+      <c r="N16">
+        <v>0.162</v>
+      </c>
+      <c r="O16">
+        <v>0.491</v>
+      </c>
+      <c r="P16">
+        <v>2.762</v>
+      </c>
+      <c r="Q16">
+        <v>2.433</v>
+      </c>
+      <c r="R16">
+        <v>0.473</v>
+      </c>
+      <c r="S16">
+        <v>0.385</v>
+      </c>
+      <c r="T16">
+        <v>0.0</v>
+      </c>
+      <c r="U16">
+        <v>0.012</v>
+      </c>
+      <c r="V16">
+        <v>0.01</v>
+      </c>
+      <c r="W16">
+        <v>0.035</v>
+      </c>
+      <c r="X16">
+        <v>0.041</v>
+      </c>
+      <c r="Y16">
+        <v>0.079</v>
+      </c>
+      <c r="Z16">
+        <v>0.069</v>
+      </c>
+      <c r="AA16">
+        <v>0.092</v>
+      </c>
+      <c r="AB16">
+        <v>0.069</v>
+      </c>
+      <c r="AC16">
+        <v>0.103</v>
+      </c>
+      <c r="AD16">
+        <v>0.075</v>
+      </c>
+      <c r="AE16">
         <v>0.08</v>
       </c>
-      <c r="AF11">
-        <v>0.052</v>
-      </c>
-      <c r="AG11">
-        <v>0.055</v>
-      </c>
-      <c r="AH11">
-        <v>0.037</v>
-      </c>
-      <c r="AI11">
-        <v>0.035</v>
-      </c>
-      <c r="AJ11">
-        <v>0.021</v>
-      </c>
-      <c r="AK11">
-        <v>0.024</v>
-      </c>
-      <c r="AL11">
-        <v>0.012</v>
-      </c>
-      <c r="AM11">
-        <v>0.012</v>
-      </c>
-      <c r="AN11">
-        <v>0.022</v>
+      <c r="AF16">
+        <v>0.06</v>
+      </c>
+      <c r="AG16">
+        <v>0.07</v>
+      </c>
+      <c r="AH16">
+        <v>0.045</v>
+      </c>
+      <c r="AI16">
+        <v>0.045</v>
+      </c>
+      <c r="AJ16">
+        <v>0.027</v>
+      </c>
+      <c r="AK16">
+        <v>0.028</v>
+      </c>
+      <c r="AL16">
+        <v>0.014</v>
+      </c>
+      <c r="AM16">
+        <v>0.016</v>
+      </c>
+      <c r="AN16">
+        <v>0.029</v>
       </c>
     </row>
   </sheetData>
